--- a/public/exports-60-250-with-coowners/29189609.xlsx
+++ b/public/exports-60-250-with-coowners/29189609.xlsx
@@ -3191,26 +3191,26 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 10</t>
+          <t xml:space="preserve">Kongevej 46</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">746491, 8463749</t>
+          <t xml:space="preserve">5791577</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J43">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3266,26 +3266,26 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Kongevej 46</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">5791577</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J44">
-        <v>230</v>
+        <v>71</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Kærbyvej 1B</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,16 +3351,16 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">746457, 10181520</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J45">
-        <v>232</v>
+        <v>160</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Lybækvej 14A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,16 +3426,16 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">10009013</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J46">
-        <v>232</v>
+        <v>90</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3491,26 +3491,26 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Ranunkelvej 15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">746579, 5790131</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J47">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3566,26 +3566,26 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Skelmosevej 20B</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6980</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">100069203</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J48">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3641,26 +3641,26 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J49">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3716,26 +3716,26 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Skolegade 34</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6940</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">4419703</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J50">
-        <v>178</v>
+        <v>242</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3791,17 +3791,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Skolevænget 31A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">4476997</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="J51">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3866,26 +3866,26 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Skovvej 25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3941,26 +3941,26 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgaardsvej 7</t>
+          <t xml:space="preserve">Skovvej 25A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463749</t>
+          <t xml:space="preserve">746237, 10047861</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J53">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4016,17 +4016,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevej 46</t>
+          <t xml:space="preserve">Storegade 40A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5791577</t>
+          <t xml:space="preserve">4468042</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="J54">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevej 46</t>
+          <t xml:space="preserve">Strandvejen 18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,16 +4101,16 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5791577</t>
+          <t xml:space="preserve">746565, 4481209</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
       <c r="J55">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4166,26 +4166,26 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærbyvej 1B</t>
+          <t xml:space="preserve">Svinget 1G</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">746457, 10181520</t>
+          <t xml:space="preserve">5788498</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J56">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4241,26 +4241,26 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lybækvej 14A</t>
+          <t xml:space="preserve">Svinget 4A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">10009013</t>
+          <t xml:space="preserve">5788486</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J57">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4316,26 +4316,26 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ranunkelvej 15</t>
+          <t xml:space="preserve">Ternevej 4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">746579, 5790131</t>
+          <t xml:space="preserve">7593289</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J58">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4391,26 +4391,26 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skelmosevej 20B</t>
+          <t xml:space="preserve">Vardevej 47A</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">6980</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100069203</t>
+          <t xml:space="preserve">5792458</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J59">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4466,26 +4466,26 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Vardevej 86</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">5792712</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4541,26 +4541,26 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 34</t>
+          <t xml:space="preserve">Vesterhavsvej 72</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6940</t>
+          <t xml:space="preserve">6990</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4419703</t>
+          <t xml:space="preserve">7636857</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J61">
-        <v>242</v>
+        <v>107</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 31A</t>
+          <t xml:space="preserve">Vikingevej 7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4476997</t>
+          <t xml:space="preserve">746290, 8433131</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="J62">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4691,17 +4691,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25</t>
+          <t xml:space="preserve">Vikingevej 7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">746290, 8433131</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="J63">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4766,26 +4766,26 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 25A</t>
+          <t xml:space="preserve">Vikingevej 7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6893</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">746237, 10047861</t>
+          <t xml:space="preserve">746290, 8433131</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J64">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4841,17 +4841,17 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 40A</t>
+          <t xml:space="preserve">Bredgade 1</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468042</t>
+          <t xml:space="preserve">4483953</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,26 +4860,26 @@
         </is>
       </c>
       <c r="J65">
-        <v>152</v>
+        <v>195</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011801</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-24</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -4916,45 +4916,45 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 18</t>
+          <t xml:space="preserve">Engdraget 22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">746565, 4481209</t>
+          <t xml:space="preserve">9722833</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J66">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200011880</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-03-26</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -4991,45 +4991,45 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 1G</t>
+          <t xml:space="preserve">Smedegade 7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788498</t>
+          <t xml:space="preserve">5724932</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200012990</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-04-28</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5066,45 +5066,45 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svinget 4A</t>
+          <t xml:space="preserve">Søibergsvej 4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5788486</t>
+          <t xml:space="preserve">5726631</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J68">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014305</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-29</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5141,45 +5141,45 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 4</t>
+          <t xml:space="preserve">Egevej 5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7593289</t>
+          <t xml:space="preserve">4468558</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J69">
-        <v>70</v>
+        <v>195</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100124780</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5216,45 +5216,45 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 47A</t>
+          <t xml:space="preserve">Enghavevej 49</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792458</t>
+          <t xml:space="preserve">5725421</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J70">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100124776</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-22</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5291,17 +5291,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 86</t>
+          <t xml:space="preserve">Søndergade 67</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5792712</t>
+          <t xml:space="preserve">4480605</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5310,26 +5310,26 @@
         </is>
       </c>
       <c r="J71">
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100124985</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-24</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterhavsvej 72</t>
+          <t xml:space="preserve">Søndergade 69</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">6990</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">7636857</t>
+          <t xml:space="preserve">4480604</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,26 +5385,26 @@
         </is>
       </c>
       <c r="J72">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100124968</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-24</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingevej 7</t>
+          <t xml:space="preserve">Kirkegade 3C</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">746290, 8433131</t>
+          <t xml:space="preserve">1805508</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J73">
-        <v>69</v>
+        <v>246</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200033020</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-06-25</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingevej 7</t>
+          <t xml:space="preserve">Østerbyvej 3B</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">746290, 8433131</t>
+          <t xml:space="preserve">747187, 100073869</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311125157</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-07-15</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5591,50 +5591,50 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vikingevej 7</t>
+          <t xml:space="preserve">Herningvej 107</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">6893</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">746290, 8433131</t>
+          <t xml:space="preserve">4429258</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>159</v>
+        <v>211</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311260253</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2027-07-11</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 1</t>
+          <t xml:space="preserve">Ternevej 4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,40 +5676,40 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4483953</t>
+          <t xml:space="preserve">7593289</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J76">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011801</t>
+          <t xml:space="preserve">311288413</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve">Botjek Center Midt- og Vestjylland</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-24</t>
+          <t xml:space="preserve">2027-12-12</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5741,50 +5741,50 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engdraget 22</t>
+          <t xml:space="preserve">Klostervej 87</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722833</t>
+          <t xml:space="preserve">4421250</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J77">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">200011880</t>
+          <t xml:space="preserve">311311426</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-03-26</t>
+          <t xml:space="preserve">2028-05-01</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5816,17 +5816,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegade 7</t>
+          <t xml:space="preserve">Bindesbølvej 2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6880</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5724932</t>
+          <t xml:space="preserve">4466575</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,31 +5835,31 @@
         </is>
       </c>
       <c r="J78">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">200012990</t>
+          <t xml:space="preserve">311424214</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve">Scanenergi A/S</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-04-28</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
+          <t xml:space="preserve">HENRY KJELDSEN. RINGKØBING TØMMERHANDEL A/S</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søibergsvej 4</t>
+          <t xml:space="preserve">Vesterled 6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,40 +5901,40 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5726631</t>
+          <t xml:space="preserve">746440, 7003908</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J79">
-        <v>225</v>
+        <v>146</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014305</t>
+          <t xml:space="preserve">311605015</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Århus)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-29</t>
+          <t xml:space="preserve">2032-06-02</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -5966,50 +5966,50 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevej 5</t>
+          <t xml:space="preserve">Holmegaardsbakken 18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4468558</t>
+          <t xml:space="preserve">335032</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J80">
-        <v>195</v>
+        <v>116</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124780</t>
+          <t xml:space="preserve">311653077</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2033-01-09</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6041,50 +6041,50 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enghavevej 49</t>
+          <t xml:space="preserve">Agervej 4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6900</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725421</t>
+          <t xml:space="preserve">8427359</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J81">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124776</t>
+          <t xml:space="preserve">311679352</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-22</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 67</t>
+          <t xml:space="preserve">Nørlundvej 2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,40 +6126,40 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480605</t>
+          <t xml:space="preserve">4486943</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J82">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124985</t>
+          <t xml:space="preserve">311679351</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-24</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 69</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4480604</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,31 +6210,31 @@
         </is>
       </c>
       <c r="J83">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124968</t>
+          <t xml:space="preserve">311892266</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holstebro Arkitektkontor ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-24</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6266,50 +6266,50 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 3C</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805508</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J84">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033020</t>
+          <t xml:space="preserve">311892266</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-25</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6341,50 +6341,50 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerbyvej 3B</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">747187, 100073869</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J85">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311125157</t>
+          <t xml:space="preserve">311892268</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-15</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6416,40 +6416,40 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herningvej 107</t>
+          <t xml:space="preserve">Ladegårdsvej 5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6920</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4429258</t>
+          <t xml:space="preserve">4410536</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J86">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311260253</t>
+          <t xml:space="preserve">311892268</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-11</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,40 +6491,40 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 4</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7593289</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J87">
-        <v>198</v>
+        <v>125</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288413</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Center Midt- og Vestjylland</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-12</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,40 +6566,40 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervej 87</t>
+          <t xml:space="preserve">Skolevej 2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6950</t>
+          <t xml:space="preserve">6960</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4421250</t>
+          <t xml:space="preserve">9690066</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J88">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311311426</t>
+          <t xml:space="preserve">311892264</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-01</t>
+          <t xml:space="preserve">2036-04-07</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,40 +6641,40 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bindesbølvej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">6880</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4466575</t>
+          <t xml:space="preserve">746491, 8463749</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J89">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424214</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HENRY KJELDSEN. RINGKØBING TØMMERHANDEL A/S</t>
+          <t xml:space="preserve">Ringkøbing-Skjern Kommune</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 6</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,30 +6726,30 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">746440, 7003908</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>146</v>
+        <v>230</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605015</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-02</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmegaardsbakken 18</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,20 +6801,20 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">335032</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J91">
-        <v>116</v>
+        <v>232</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653077</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-09</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,40 +6866,40 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agervej 4</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6900</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8427359</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J92">
-        <v>99</v>
+        <v>232</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679352</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,40 +6941,40 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørlundvej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4486943</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J93">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679351</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,40 +7016,40 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J94">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892266</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,40 +7091,40 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J95">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892266</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,40 +7166,40 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J96">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892268</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,40 +7241,40 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ladegårdsvej 5</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6920</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4410536</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J97">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892268</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,40 +7316,40 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J98">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,40 +7391,40 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 2</t>
+          <t xml:space="preserve">Kjærgaardsvej 7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6960</t>
+          <t xml:space="preserve">6950</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9690066</t>
+          <t xml:space="preserve">8463749</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J99">
-        <v>128</v>
+        <v>237</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892264</t>
+          <t xml:space="preserve">311930128</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-07</t>
+          <t xml:space="preserve">2036-10-06</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
